--- a/google play/reports/eda_section_e_workbook.xlsx
+++ b/google play/reports/eda_section_e_workbook.xlsx
@@ -435,7 +435,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5857999803323828</v>
+        <v>0.2553016453382084</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5971088602615793</v>
+        <v>0.3094149908592322</v>
       </c>
     </row>
     <row r="5">
@@ -510,18 +510,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>awesome and easy</t>
+          <t>Just standard game, not as advertised.</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -529,7 +529,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5453a021bcd879d4c878f1e2684bcb9c</t>
+          <t>1add3207b5305f4e402de5565985f4b7</t>
         </is>
       </c>
     </row>
@@ -539,18 +539,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>enjoy this app</t>
+          <t>Have to play too many levels to reach Kings Nightmare level.😞</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -558,7 +558,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3310ba09cd7d9355041c1ce9e2d36516</t>
+          <t>bb802725101f6bb9c2bb9563cbb5c866</t>
         </is>
       </c>
     </row>
@@ -568,18 +568,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>so good as I thought it is more better than it I love ittt</t>
+          <t>it is a very fun game</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -587,7 +587,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ba2dec48547d5bfc7f9acd82569c53cf</t>
+          <t>22b77ca31d59ba80ee474811d2656e84</t>
         </is>
       </c>
     </row>
@@ -597,18 +597,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I use this app all the time, it's the best! Far superior to other recording apps I've tried.</t>
+          <t>it's a 5 ✨ rating and a 💯 percent rating and again thank you.</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -616,7 +616,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>497f8ec0d8e33e85c514c4e0af347b0f</t>
+          <t>b9ba1aa812536d468c155813f22bead4</t>
         </is>
       </c>
     </row>
@@ -626,18 +626,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>works ok,so far</t>
+          <t>good time pass</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -645,7 +645,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0642694ed4ac9225f6e418a9da479f8a</t>
+          <t>7cfa7d20d9e3c012bd1b47fd9d31a886</t>
         </is>
       </c>
     </row>
@@ -655,18 +655,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>this is so fun</t>
+          <t>It's stupid that the propeller decides where it wants to go hit especially when paired with the TNT. why can't it be controlled? 🤷🏾‍♂️</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -674,7 +674,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>312454bf444531069a8036686d2a9ffd</t>
+          <t>45f89035b480fd9b36fa135dd39a7d4d</t>
         </is>
       </c>
     </row>
@@ -684,18 +684,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Improved lots since 2023. Can change location to SD card, audio source, bitrate, format (mp3/mp4/wav) &amp; gain. Can record internal audio, incl. &amp; excluding mic. Can mark, resume, disregard, trim, alter, compress, trash, backup &amp; share recording. Can quick record via quick panel. Option to use Bluetooth mic via one-time unlock ($14). v1.3.4.1 is worth it. Only thing would be specifying audio source. Not sure difference btwn Default, Main &amp; Main (unprocessed). Back (cam)? Front (Top or Bottom mic)?</t>
+          <t>stupidly annoying</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -703,7 +703,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>d5d8a3977b1431ceaed5e1adf34f3d26</t>
+          <t>d6ffbc4c356b1e47a0bbd1eaa3be0b7d</t>
         </is>
       </c>
     </row>
@@ -713,18 +713,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>easy and efficient. works great for humming my melodies and then listening later to make my songs.</t>
+          <t>This is a really fun game however there are way too many very hard levels that takes such a long time to play that it actually takes the fun out of it. I probably won't be playing much longer.</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -732,7 +732,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2f2795b4c9a6ed926615d02a0a6bc3e6</t>
+          <t>9749faca8f69ecdb66bc803ac25a10eb</t>
         </is>
       </c>
     </row>
@@ -742,18 +742,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no sound seems to record but not playback</t>
+          <t>Very nice app</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -761,7 +761,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>777d8386f755cc10904fb2db970b1850</t>
+          <t>1e8b0be4b90489c41f05caf1dd940ebf</t>
         </is>
       </c>
     </row>
@@ -771,18 +771,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>271</v>
+        <v>26</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wonderful app! Recorded myself singing. The sound was crisp and clear. Record different types of meetings which allows for more options to get the right range of recordings that for that particular environment. Compress files and send them to Drive. Wonderful. Thank you!</t>
+          <t>this is a pretty good game</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -790,7 +790,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>c477239943642a061f77328d7d6a0c6e</t>
+          <t>ce82d03f3e9c76b29f4c64b65cd06ee4</t>
         </is>
       </c>
     </row>
@@ -800,18 +800,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>clear sound</t>
+          <t>im just addicted this game. 6years continuously played. no bore</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -819,7 +819,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>47c776506d2fc4af600aa76dd4505166</t>
+          <t>03961f80a3c549c4fdb835899afe569f</t>
         </is>
       </c>
     </row>
@@ -829,18 +829,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>the best voice recorder app I have experience so far and I have tried many of them!</t>
+          <t>my app keep crashing. did everything you suggested but it still crashing</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -848,7 +848,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>67cd053133fac721ab47e222b23403ed</t>
+          <t>c2e20e750395fbd3ad08b70b8f833902</t>
         </is>
       </c>
     </row>
@@ -858,18 +858,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>192</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>it's great</t>
+          <t>I'm sick of all these games that advertise the game to be one way but then it's completely different. This is EXACTLY like royal match. It's literally the same game with different backgrounds.</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -877,7 +877,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>e099517ed63ff85f8fd8355d50eb1f34</t>
+          <t>7bec7bc6b1680a602634797867d6d12c</t>
         </is>
       </c>
     </row>
@@ -887,18 +887,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Everything is perfect 😊</t>
+          <t>Advestised game mode not to be found</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -906,7 +906,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>26cbc3d5266467c5a6c4dedcf95a6baf</t>
+          <t>68c2b014cd9ba7a388269b8f51befe6b</t>
         </is>
       </c>
     </row>
@@ -916,18 +916,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I think I've find what I needed on this app, thank u for this</t>
+          <t>just not into bombs. peace</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -935,7 +935,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>dff3b9d49044dd6fb7eae61679789a50</t>
+          <t>7b0e1a878b999310e3622ea325fcdbd7</t>
         </is>
       </c>
     </row>
@@ -945,18 +945,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>268</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>The sound it perfect</t>
+          <t>First it creates addiction, then it forces you to pay if you want to make any progress. There should be laws protecting children (and their parents) from games like this. It's like narcotics, just different kind. Don't waste your time to figure this out, just skip it.</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -964,7 +964,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3059073c823dca90c7fff6052f0573d4</t>
+          <t>70892475b54e312b79fae9cad9e05415</t>
         </is>
       </c>
     </row>
@@ -974,18 +974,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>couldnt even get the POS to download !</t>
+          <t>very nice game</t>
         </is>
       </c>
       <c r="F22" t="b">
@@ -993,7 +993,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>779e80f9ab754be3cbb213172f085017</t>
+          <t>fe31e048ac7538d40570174e27044b59</t>
         </is>
       </c>
     </row>
@@ -1003,18 +1003,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>full screen ad with fake x to close, have to kill the app to get the ad off the screen</t>
+          <t>Updates every Monday is the only fine matter about the game.</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>b930373bcc4f42dc8c705e6b329dc771</t>
+          <t>8fc77ea7b9e16fe09e23880e7458c2f5</t>
         </is>
       </c>
     </row>
@@ -1032,18 +1032,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>worked perfectly.</t>
+          <t>great game</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>9091662a512bc3a67a0d64e19a361c3b</t>
+          <t>d83769e2937e56c922fadeb91a512422</t>
         </is>
       </c>
     </row>
@@ -1061,18 +1061,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Voice Recorder Audio Sound MP3</t>
+          <t>Royal Match</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Live transcribe is behind a wall, when you could use somejing else that already transcribes...</t>
+          <t>good game horrendous amount of ads.</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>dcba26d750825a42f8b97dc9e79e40b6</t>
+          <t>e6b591fd2720d232e4942bf3fba3f271</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5857999803323828</v>
+        <v>0.2553016453382084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5971088602615793</v>
+        <v>0.3094149908592322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
